--- a/survey_templates/037_program_member_satisfaction_assessment_form--survey_templates.xlsx
+++ b/survey_templates/037_program_member_satisfaction_assessment_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_1</t>
+          <t>recommendation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>How likely are you to recommend our program to a friend</t>
+          <t>How likely are you to recommend our program to a friend?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_2</t>
+          <t>overall_satisfaction</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How satisfied are you with our program</t>
+          <t>How satisfied are you with the program overall?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_3</t>
+          <t>participation_likelihood</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How likely are you to continue participating in our program</t>
+          <t>How likely are you to continue participating in our program?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>program_participation</t>
+          <t>participation_duration</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Program Participation</t>
+          <t>What is your program participation duration?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>program_participation_time</t>
+          <t>participation_start</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Program Participation Time</t>
+          <t>What is your program participation start date?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>program_feedback</t>
+          <t>participation_end</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Program Feedback</t>
+          <t>What is your program participation end date?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_4</t>
+          <t>participation_frequency</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How satisfied are you with the program overall</t>
+          <t>What is your program participation frequency?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>program_participation_frequency</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Program Participation Frequency</t>
+          <t>What feedback do you have for the program?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>program_participation_duration</t>
+          <t>overall_satisfaction_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Program Participation Duration</t>
+          <t>Overall Satisfaction 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>program_participation_start</t>
+          <t>future_participation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Program Participation Start</t>
+          <t>How likely are you to participate in our program in the future?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>program_participation_end</t>
+          <t>fees</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Program Participation End</t>
+          <t>What is your program participation fee?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_5</t>
+          <t>participation_time</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Overall Satisfaction</t>
+          <t>What is your program participation time?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,315 +819,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_6</t>
+          <t>satisfaction_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How satisfied are you with the program overall</t>
+          <t>How satisfied are you with the program content?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>program_participation</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Program Participation</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>program_participation_time</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Program Participation Time</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>program_feedback</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Program Feedback</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>program_participation_frequency</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Program Participation Frequency</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>program_participation_duration</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Program Participation Duration</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>program_participation_start</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Program Participation Start</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>program_participation_end</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Program Participation End</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>program_member_satisfaction_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>How likely are you to participate in our program again</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>program_participation_fees</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Program Participation Fees</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>program_participation_cost</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Program Participation Cost</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>program_participation_fees_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Program Participation Fees 2</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>program_participation_cost_2</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Program Participation Cost 2</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>program_member_satisfaction_3</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>How likely are you to participate in our program in the future</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1144,12 +845,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1172,408 +873,459 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_1_choices</t>
+          <t>recommendation_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_1_choices</t>
+          <t>recommendation_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_1_choices</t>
+          <t>recommendation_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Not Likely</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_2_choices</t>
+          <t>recommendation_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Not At All Likely</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_2_choices</t>
+          <t>overall_satisfaction_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_2_choices</t>
+          <t>overall_satisfaction_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_3_choices</t>
+          <t>overall_satisfaction_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_3_choices</t>
+          <t>overall_satisfaction_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_3_choices</t>
+          <t>overall_satisfaction_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_4_choices</t>
+          <t>participation_likelihood_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_4_choices</t>
+          <t>participation_likelihood_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_4_choices</t>
+          <t>participation_likelihood_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Not Likely</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_5_choices</t>
+          <t>participation_likelihood_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Not At All Likely</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_5_choices</t>
+          <t>overall_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_5_choices</t>
+          <t>overall_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_6_choices</t>
+          <t>overall_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_6_choices</t>
+          <t>overall_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_6_choices</t>
+          <t>overall_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_2_choices</t>
+          <t>future_participation_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_2_choices</t>
+          <t>future_participation_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_2_choices</t>
+          <t>future_participation_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Not Likely</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_3_choices</t>
+          <t>future_participation_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Not At All Likely</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_3_choices</t>
+          <t>satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>program_member_satisfaction_3_choices</t>
+          <t>satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Somewhat Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>satisfaction_2_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>satisfaction_2_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>somewhat_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Somewhat Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>satisfaction_2_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>very_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
